--- a/submission/COMAVI_v7.15_SI/S1_Table.xlsx
+++ b/submission/COMAVI_v7.15_SI/S1_Table.xlsx
@@ -489,7 +489,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I101"/>
+  <dimension ref="A1:I102"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="18" customWidth="1" min="1" max="1"/>
@@ -509,7 +509,6 @@
         </is>
       </c>
     </row>
-    <row r="2"/>
     <row r="3">
       <c r="A3" s="1" t="inlineStr">
         <is>
@@ -731,7 +730,7 @@
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>WT-like BARD1 interaction by Y2H</t>
+          <t>WT-like BARD1 interaction by Y2H: score 1.025 (95% CI 0.840-1.213), permutation p = 0.58, but the measurement is below the source's own 800-read filter and is reported here with that caveat</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
@@ -872,7 +871,7 @@
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>WT-like BARD1 interaction by Y2H</t>
+          <t>WT-like BARD1 interaction by Y2H: score 1.019 (95% CI 0.983-1.056), passes the source's 800-read filter</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
@@ -2188,7 +2187,7 @@
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>Hb Kansas: alpha1-beta2 H-bond loss, reduced tetramer assembly energy (~1.5 kcal/mol)</t>
+          <t>Hb Kansas: alpha1-beta2 H-bond loss. Source reports Kd(tetramer-&gt;dimer) ~1.0-1.4 uM for normal oxyhemoglobin against ~200 uM, giving a reduced tetramer assembly energy of 3.0 kcal/mol per tetramer (1.5 per interface); stated per tetramer to match the beta-W37 series</t>
         </is>
       </c>
       <c r="H38" t="inlineStr">
@@ -2643,12 +2642,12 @@
       </c>
       <c r="D48" t="inlineStr">
         <is>
-          <t>neutral</t>
+          <t>destab</t>
         </is>
       </c>
       <c r="E48" t="inlineStr">
         <is>
-          <t>E3_qualitative_experimental</t>
+          <t>E1_quantitative_energetic</t>
         </is>
       </c>
       <c r="F48" t="inlineStr">
@@ -2658,12 +2657,12 @@
       </c>
       <c r="G48" t="inlineStr">
         <is>
-          <t>WT-like RAF1 binding; impaired GTP hydrolysis. G12 is 13.6 A from RAF1</t>
+          <t>RAF-RBD affinity decreased 4.8-fold (270 +/- 46 nmol/L against 56 +/- 6 for wild type). Measured magnitude 0.93 kcal/mol, below the 2.5 kcal/mol reference threshold</t>
         </is>
       </c>
       <c r="H48" t="inlineStr">
         <is>
-          <t>Hunter 2015</t>
+          <t>Hunter 2015 Mol Cancer Res 13:1325 Table 2 (doi:10.1158/1541-7786.MCR-15-0203)</t>
         </is>
       </c>
       <c r="I48" t="inlineStr">
@@ -2690,12 +2689,12 @@
       </c>
       <c r="D49" t="inlineStr">
         <is>
-          <t>neutral</t>
+          <t>destab</t>
         </is>
       </c>
       <c r="E49" t="inlineStr">
         <is>
-          <t>E3_qualitative_experimental</t>
+          <t>E1_quantitative_energetic</t>
         </is>
       </c>
       <c r="F49" t="inlineStr">
@@ -2705,12 +2704,12 @@
       </c>
       <c r="G49" t="inlineStr">
         <is>
-          <t>WT-like RAF1 binding; impaired GTP hydrolysis</t>
+          <t>RAF-RBD affinity decreased 7.3-fold (411 +/- 40 nmol/L against 56 +/- 6 for wild type). Measured magnitude 1.18 kcal/mol, below the 2.5 kcal/mol reference threshold</t>
         </is>
       </c>
       <c r="H49" t="inlineStr">
         <is>
-          <t>Hunter 2015</t>
+          <t>Hunter 2015 Mol Cancer Res 13:1325 Table 2 (doi:10.1158/1541-7786.MCR-15-0203)</t>
         </is>
       </c>
       <c r="I49" t="inlineStr">
@@ -2757,7 +2756,7 @@
       </c>
       <c r="H50" t="inlineStr">
         <is>
-          <t>Hunter 2015</t>
+          <t>Hunter 2015 Mol Cancer Res 13:1325 Table 2 (doi:10.1158/1541-7786.MCR-15-0203)</t>
         </is>
       </c>
       <c r="I50" t="inlineStr">
@@ -2809,7 +2808,7 @@
       </c>
       <c r="I51" t="inlineStr">
         <is>
-          <t>[57, 58]</t>
+          <t>[57]</t>
         </is>
       </c>
     </row>
@@ -2856,7 +2855,7 @@
       </c>
       <c r="I52" t="inlineStr">
         <is>
-          <t>[57, 58]</t>
+          <t>[57]</t>
         </is>
       </c>
     </row>
@@ -2903,7 +2902,7 @@
       </c>
       <c r="I53" t="inlineStr">
         <is>
-          <t>[57, 58]</t>
+          <t>[57]</t>
         </is>
       </c>
     </row>
@@ -3009,42 +3008,42 @@
       </c>
       <c r="B56" t="inlineStr">
         <is>
-          <t>K618E</t>
+          <t>H718Y</t>
         </is>
       </c>
       <c r="C56" t="inlineStr">
         <is>
-          <t>binding</t>
+          <t>monomer</t>
         </is>
       </c>
       <c r="D56" t="inlineStr">
         <is>
-          <t>neutral</t>
+          <t>destab</t>
         </is>
       </c>
       <c r="E56" t="inlineStr">
         <is>
-          <t>E3_qualitative_experimental</t>
+          <t>E2_quantitative_functional</t>
         </is>
       </c>
       <c r="F56" t="inlineStr">
         <is>
-          <t>coupled</t>
+          <t>direct</t>
         </is>
       </c>
       <c r="G56" t="inlineStr">
         <is>
-          <t>Non-damaging in functional assay</t>
+          <t>Source states H718Y moderately destabilizes the MLH1 protein; thermal stability decreased more strongly in V716M, H718Y and E578G, and pulse-chase half-life fell to 64% of wild type. Clinically neutral</t>
         </is>
       </c>
       <c r="H56" t="inlineStr">
         <is>
-          <t>Drost 2019 (functional assay)</t>
+          <t>Hinrichsen 2013 Clin Cancer Res 19:2432 (doi:10.1158/1078-0432.CCR-12-3299)</t>
         </is>
       </c>
       <c r="I56" t="inlineStr">
         <is>
-          <t>[34]</t>
+          <t>see evidence_citation</t>
         </is>
       </c>
     </row>
@@ -3056,7 +3055,7 @@
       </c>
       <c r="B57" t="inlineStr">
         <is>
-          <t>L749P</t>
+          <t>K618E</t>
         </is>
       </c>
       <c r="C57" t="inlineStr">
@@ -3066,32 +3065,32 @@
       </c>
       <c r="D57" t="inlineStr">
         <is>
-          <t>destab</t>
+          <t>neutral</t>
         </is>
       </c>
       <c r="E57" t="inlineStr">
         <is>
-          <t>E2_quantitative_functional</t>
+          <t>E3_qualitative_experimental</t>
         </is>
       </c>
       <c r="F57" t="inlineStr">
         <is>
-          <t>direct</t>
+          <t>coupled</t>
         </is>
       </c>
       <c r="G57" t="inlineStr">
         <is>
-          <t>PMS2 co-IP 30% of WT</t>
+          <t>Non-damaging in functional assay</t>
         </is>
       </c>
       <c r="H57" t="inlineStr">
         <is>
-          <t>Kosinski 2010 (PMS2 co-IP, MMR activity)</t>
+          <t>Drost 2019 (functional assay)</t>
         </is>
       </c>
       <c r="I57" t="inlineStr">
         <is>
-          <t>[32]</t>
+          <t>[34]</t>
         </is>
       </c>
     </row>
@@ -3103,7 +3102,7 @@
       </c>
       <c r="B58" t="inlineStr">
         <is>
-          <t>Q542L</t>
+          <t>L749P</t>
         </is>
       </c>
       <c r="C58" t="inlineStr">
@@ -3128,7 +3127,7 @@
       </c>
       <c r="G58" t="inlineStr">
         <is>
-          <t>PMS2 co-IP 54% of WT</t>
+          <t>PMS2 co-IP 30% of WT</t>
         </is>
       </c>
       <c r="H58" t="inlineStr">
@@ -3150,7 +3149,7 @@
       </c>
       <c r="B59" t="inlineStr">
         <is>
-          <t>R755W</t>
+          <t>Q542L</t>
         </is>
       </c>
       <c r="C59" t="inlineStr">
@@ -3160,7 +3159,7 @@
       </c>
       <c r="D59" t="inlineStr">
         <is>
-          <t>neutral</t>
+          <t>destab</t>
         </is>
       </c>
       <c r="E59" t="inlineStr">
@@ -3175,12 +3174,12 @@
       </c>
       <c r="G59" t="inlineStr">
         <is>
-          <t>MAVE interaction score +0.617; PMS2 co-IP 82% -- binding preserved</t>
+          <t>PMS2 co-IP 54% of WT</t>
         </is>
       </c>
       <c r="H59" t="inlineStr">
         <is>
-          <t>MAVE abundance/interaction scores; Kosinski 2010 co-IP</t>
+          <t>Kosinski 2010 (PMS2 co-IP, MMR activity)</t>
         </is>
       </c>
       <c r="I59" t="inlineStr">
@@ -3202,12 +3201,12 @@
       </c>
       <c r="C60" t="inlineStr">
         <is>
-          <t>fold_complex</t>
+          <t>binding</t>
         </is>
       </c>
       <c r="D60" t="inlineStr">
         <is>
-          <t>destab</t>
+          <t>neutral</t>
         </is>
       </c>
       <c r="E60" t="inlineStr">
@@ -3222,7 +3221,7 @@
       </c>
       <c r="G60" t="inlineStr">
         <is>
-          <t>MAVE abundance score -0.334: reduced cellular abundance</t>
+          <t>MAVE interaction score +0.617; PMS2 co-IP 82% -- binding preserved</t>
         </is>
       </c>
       <c r="H60" t="inlineStr">
@@ -3249,7 +3248,7 @@
       </c>
       <c r="C61" t="inlineStr">
         <is>
-          <t>monomer</t>
+          <t>fold_complex</t>
         </is>
       </c>
       <c r="D61" t="inlineStr">
@@ -3291,42 +3290,42 @@
       </c>
       <c r="B62" t="inlineStr">
         <is>
-          <t>V384D</t>
+          <t>R755W</t>
         </is>
       </c>
       <c r="C62" t="inlineStr">
         <is>
-          <t>binding</t>
+          <t>monomer</t>
         </is>
       </c>
       <c r="D62" t="inlineStr">
         <is>
-          <t>neutral</t>
+          <t>destab</t>
         </is>
       </c>
       <c r="E62" t="inlineStr">
         <is>
-          <t>E3_qualitative_experimental</t>
+          <t>E2_quantitative_functional</t>
         </is>
       </c>
       <c r="F62" t="inlineStr">
         <is>
-          <t>coupled</t>
+          <t>direct</t>
         </is>
       </c>
       <c r="G62" t="inlineStr">
         <is>
-          <t>Reclassified non-pathogenic; MMR-proficient</t>
+          <t>MAVE abundance score -0.334: reduced cellular abundance</t>
         </is>
       </c>
       <c r="H62" t="inlineStr">
         <is>
-          <t>InSiGHT expert-panel reclassification; rs63750447 AF ~8.9% EAS</t>
+          <t>MAVE abundance/interaction scores; Kosinski 2010 co-IP</t>
         </is>
       </c>
       <c r="I62" t="inlineStr">
         <is>
-          <t>[35]</t>
+          <t>[32]</t>
         </is>
       </c>
     </row>
@@ -3343,7 +3342,7 @@
       </c>
       <c r="C63" t="inlineStr">
         <is>
-          <t>fold_complex</t>
+          <t>binding</t>
         </is>
       </c>
       <c r="D63" t="inlineStr">
@@ -3353,17 +3352,17 @@
       </c>
       <c r="E63" t="inlineStr">
         <is>
-          <t>E5_inferred_no_axis_assay</t>
+          <t>E3_qualitative_experimental</t>
         </is>
       </c>
       <c r="F63" t="inlineStr">
         <is>
-          <t>inferred</t>
+          <t>coupled</t>
         </is>
       </c>
       <c r="G63" t="inlineStr">
         <is>
-          <t>No assembly-context stability measurement; token inferred from the intact monomer fold</t>
+          <t>Reclassified non-pathogenic; MMR-proficient</t>
         </is>
       </c>
       <c r="H63" t="inlineStr">
@@ -3390,7 +3389,7 @@
       </c>
       <c r="C64" t="inlineStr">
         <is>
-          <t>monomer</t>
+          <t>fold_complex</t>
         </is>
       </c>
       <c r="D64" t="inlineStr">
@@ -3410,7 +3409,7 @@
       </c>
       <c r="G64" t="inlineStr">
         <is>
-          <t>No subunit-stability assay; token inferred</t>
+          <t>No assembly-context stability measurement; token inferred from the intact monomer fold</t>
         </is>
       </c>
       <c r="H64" t="inlineStr">
@@ -3427,17 +3426,17 @@
     <row r="65">
       <c r="A65" t="inlineStr">
         <is>
-          <t>msh2_msh6</t>
+          <t>mlh1_pms2</t>
         </is>
       </c>
       <c r="B65" t="inlineStr">
         <is>
-          <t>A636P</t>
+          <t>V384D</t>
         </is>
       </c>
       <c r="C65" t="inlineStr">
         <is>
-          <t>binding</t>
+          <t>monomer</t>
         </is>
       </c>
       <c r="D65" t="inlineStr">
@@ -3447,27 +3446,27 @@
       </c>
       <c r="E65" t="inlineStr">
         <is>
-          <t>E3_qualitative_experimental</t>
+          <t>E5_inferred_no_axis_assay</t>
         </is>
       </c>
       <c r="F65" t="inlineStr">
         <is>
-          <t>direct</t>
+          <t>inferred</t>
         </is>
       </c>
       <c r="G65" t="inlineStr">
         <is>
-          <t>MSH2-MSH6 interaction intact; ATPase mismatch binding/release defect</t>
+          <t>No subunit-stability assay; token inferred</t>
         </is>
       </c>
       <c r="H65" t="inlineStr">
         <is>
-          <t>Ollila 2008 Hum Mutat 29:1355 (PMID 18951462); Ollila 2006 Gastroenterology (PMID 17101317)</t>
+          <t>InSiGHT expert-panel reclassification; rs63750447 AF ~8.9% EAS</t>
         </is>
       </c>
       <c r="I65" t="inlineStr">
         <is>
-          <t>[37, 38]</t>
+          <t>[35]</t>
         </is>
       </c>
     </row>
@@ -3484,7 +3483,7 @@
       </c>
       <c r="C66" t="inlineStr">
         <is>
-          <t>fold_complex</t>
+          <t>binding</t>
         </is>
       </c>
       <c r="D66" t="inlineStr">
@@ -3531,7 +3530,7 @@
       </c>
       <c r="C67" t="inlineStr">
         <is>
-          <t>monomer</t>
+          <t>fold_complex</t>
         </is>
       </c>
       <c r="D67" t="inlineStr">
@@ -3551,7 +3550,7 @@
       </c>
       <c r="G67" t="inlineStr">
         <is>
-          <t>MSH2 expression/stability preserved; ATPase mismatch binding/release defect</t>
+          <t>MSH2-MSH6 interaction intact; ATPase mismatch binding/release defect</t>
         </is>
       </c>
       <c r="H67" t="inlineStr">
@@ -3573,12 +3572,12 @@
       </c>
       <c r="B68" t="inlineStr">
         <is>
-          <t>C697F</t>
+          <t>A636P</t>
         </is>
       </c>
       <c r="C68" t="inlineStr">
         <is>
-          <t>binding</t>
+          <t>monomer</t>
         </is>
       </c>
       <c r="D68" t="inlineStr">
@@ -3598,7 +3597,7 @@
       </c>
       <c r="G68" t="inlineStr">
         <is>
-          <t>ATPase catalytic defect, protein stable, interaction intact</t>
+          <t>MSH2 expression/stability preserved; ATPase mismatch binding/release defect</t>
         </is>
       </c>
       <c r="H68" t="inlineStr">
@@ -3620,7 +3619,7 @@
       </c>
       <c r="B69" t="inlineStr">
         <is>
-          <t>G322D</t>
+          <t>C697F</t>
         </is>
       </c>
       <c r="C69" t="inlineStr">
@@ -3645,7 +3644,7 @@
       </c>
       <c r="G69" t="inlineStr">
         <is>
-          <t>MMR-proficient with interaction intact; gnomAD ~1.9%</t>
+          <t>ATPase catalytic defect, protein stable, interaction intact</t>
         </is>
       </c>
       <c r="H69" t="inlineStr">
@@ -3667,7 +3666,7 @@
       </c>
       <c r="B70" t="inlineStr">
         <is>
-          <t>G674R</t>
+          <t>G322D</t>
         </is>
       </c>
       <c r="C70" t="inlineStr">
@@ -3692,17 +3691,17 @@
       </c>
       <c r="G70" t="inlineStr">
         <is>
-          <t>MSH6 binding preserved by co-IP; MMR lost via Walker-A ATPase defect</t>
+          <t>MMR-proficient with interaction intact; gnomAD ~1.9%</t>
         </is>
       </c>
       <c r="H70" t="inlineStr">
         <is>
-          <t>Jia 2021</t>
+          <t>Ollila 2008 Hum Mutat 29:1355 (PMID 18951462); Ollila 2006 Gastroenterology (PMID 17101317)</t>
         </is>
       </c>
       <c r="I70" t="inlineStr">
         <is>
-          <t>[39]</t>
+          <t>[37, 38]</t>
         </is>
       </c>
     </row>
@@ -4419,7 +4418,7 @@
       </c>
       <c r="B86" t="inlineStr">
         <is>
-          <t>R361C</t>
+          <t>I500V</t>
         </is>
       </c>
       <c r="C86" t="inlineStr">
@@ -4429,12 +4428,12 @@
       </c>
       <c r="D86" t="inlineStr">
         <is>
-          <t>destab</t>
+          <t>stab</t>
         </is>
       </c>
       <c r="E86" t="inlineStr">
         <is>
-          <t>E3_qualitative_experimental</t>
+          <t>E2_quantitative_functional</t>
         </is>
       </c>
       <c r="F86" t="inlineStr">
@@ -4444,29 +4443,29 @@
       </c>
       <c r="G86" t="inlineStr">
         <is>
-          <t>Completely abolished R-Smad interaction</t>
+          <t>GST pull-down shows increased recovery of SMAD3 with SMAD4 I500V, and TR-FRET shows a statistically significant increase in SMAD4-SMAD3 interaction. R361H and R361C negative controls show the opposite direction, so the assay resolves sign</t>
         </is>
       </c>
       <c r="H86" t="inlineStr">
         <is>
-          <t>Lanauze 2021 (co-IP)</t>
+          <t>Lindsay 2025 J Allergy Clin Immunol Fig 4D-E (doi:10.1016/j.jaci.2024.08.024)</t>
         </is>
       </c>
       <c r="I86" t="inlineStr">
         <is>
-          <t>[45]</t>
+          <t>see evidence_citation</t>
         </is>
       </c>
     </row>
     <row r="87">
       <c r="A87" t="inlineStr">
         <is>
-          <t>troponin_ic</t>
+          <t>smad4_smad3</t>
         </is>
       </c>
       <c r="B87" t="inlineStr">
         <is>
-          <t>P82S</t>
+          <t>R361C</t>
         </is>
       </c>
       <c r="C87" t="inlineStr">
@@ -4476,32 +4475,32 @@
       </c>
       <c r="D87" t="inlineStr">
         <is>
-          <t>neutral</t>
+          <t>destab</t>
         </is>
       </c>
       <c r="E87" t="inlineStr">
         <is>
-          <t>E4_population_frequency</t>
+          <t>E3_qualitative_experimental</t>
         </is>
       </c>
       <c r="F87" t="inlineStr">
         <is>
-          <t>inferred</t>
+          <t>direct</t>
         </is>
       </c>
       <c r="G87" t="inlineStr">
         <is>
-          <t>AF ~3% African-American: benign by frequency</t>
+          <t>Completely abolished R-Smad interaction</t>
         </is>
       </c>
       <c r="H87" t="inlineStr">
         <is>
-          <t>Frazier 2008; gnomAD</t>
+          <t>Lanauze 2021 (co-IP)</t>
         </is>
       </c>
       <c r="I87" t="inlineStr">
         <is>
-          <t>[47, 57]</t>
+          <t>[45]</t>
         </is>
       </c>
     </row>
@@ -4518,7 +4517,7 @@
       </c>
       <c r="C88" t="inlineStr">
         <is>
-          <t>fold_complex</t>
+          <t>binding</t>
         </is>
       </c>
       <c r="D88" t="inlineStr">
@@ -4565,7 +4564,7 @@
       </c>
       <c r="C89" t="inlineStr">
         <is>
-          <t>monomer</t>
+          <t>fold_complex</t>
         </is>
       </c>
       <c r="D89" t="inlineStr">
@@ -4607,12 +4606,12 @@
       </c>
       <c r="B90" t="inlineStr">
         <is>
-          <t>R145G</t>
+          <t>P82S</t>
         </is>
       </c>
       <c r="C90" t="inlineStr">
         <is>
-          <t>binding</t>
+          <t>monomer</t>
         </is>
       </c>
       <c r="D90" t="inlineStr">
@@ -4622,27 +4621,27 @@
       </c>
       <c r="E90" t="inlineStr">
         <is>
-          <t>E2_quantitative_functional</t>
+          <t>E4_population_frequency</t>
         </is>
       </c>
       <c r="F90" t="inlineStr">
         <is>
-          <t>direct</t>
+          <t>inferred</t>
         </is>
       </c>
       <c r="G90" t="inlineStr">
         <is>
-          <t>EC50 1.4 uM vs 0.8 uM WT: reduced inhibitory potency, actin affinity unchanged -- interface retained</t>
+          <t>AF ~3% African-American: benign by frequency</t>
         </is>
       </c>
       <c r="H90" t="inlineStr">
         <is>
-          <t>Elliott 2000 JBC 275:22069; Takahashi / Kimura 2001 (PMID 11735257)</t>
+          <t>Frazier 2008; gnomAD</t>
         </is>
       </c>
       <c r="I90" t="inlineStr">
         <is>
-          <t>[46, 48]</t>
+          <t>[47, 57]</t>
         </is>
       </c>
     </row>
@@ -4654,7 +4653,7 @@
       </c>
       <c r="B91" t="inlineStr">
         <is>
-          <t>R145Q</t>
+          <t>R145G</t>
         </is>
       </c>
       <c r="C91" t="inlineStr">
@@ -4679,29 +4678,29 @@
       </c>
       <c r="G91" t="inlineStr">
         <is>
-          <t>Same class as R145G: reduced inhibition, actin affinity unchanged</t>
+          <t>EC50 1.4 uM vs 0.8 uM WT: reduced inhibitory potency, actin affinity unchanged -- interface retained</t>
         </is>
       </c>
       <c r="H91" t="inlineStr">
         <is>
-          <t>Kimura 2001 (PMID 11735257)</t>
+          <t>Elliott 2000 JBC 275:22069; Takahashi / Kimura 2001 (PMID 11735257)</t>
         </is>
       </c>
       <c r="I91" t="inlineStr">
         <is>
-          <t>[48]</t>
+          <t>[46, 48]</t>
         </is>
       </c>
     </row>
     <row r="92">
       <c r="A92" t="inlineStr">
         <is>
-          <t>vhl_elonginc</t>
+          <t>troponin_ic</t>
         </is>
       </c>
       <c r="B92" t="inlineStr">
         <is>
-          <t>L158Q</t>
+          <t>R145Q</t>
         </is>
       </c>
       <c r="C92" t="inlineStr">
@@ -4711,12 +4710,12 @@
       </c>
       <c r="D92" t="inlineStr">
         <is>
-          <t>destab</t>
+          <t>neutral</t>
         </is>
       </c>
       <c r="E92" t="inlineStr">
         <is>
-          <t>E3_qualitative_experimental</t>
+          <t>E2_quantitative_functional</t>
         </is>
       </c>
       <c r="F92" t="inlineStr">
@@ -4726,17 +4725,17 @@
       </c>
       <c r="G92" t="inlineStr">
         <is>
-          <t>Disrupts VCB complex assembly</t>
+          <t>Same class as R145G: reduced inhibition, actin affinity unchanged</t>
         </is>
       </c>
       <c r="H92" t="inlineStr">
         <is>
-          <t>Stebbins 1999 Science</t>
+          <t>Kimura 2001 (PMID 11735257)</t>
         </is>
       </c>
       <c r="I92" t="inlineStr">
         <is>
-          <t>[49]</t>
+          <t>[48]</t>
         </is>
       </c>
     </row>
@@ -4753,7 +4752,7 @@
       </c>
       <c r="C93" t="inlineStr">
         <is>
-          <t>fold_complex</t>
+          <t>binding</t>
         </is>
       </c>
       <c r="D93" t="inlineStr">
@@ -4795,17 +4794,17 @@
       </c>
       <c r="B94" t="inlineStr">
         <is>
-          <t>Y98H</t>
+          <t>L158Q</t>
         </is>
       </c>
       <c r="C94" t="inlineStr">
         <is>
-          <t>binding</t>
+          <t>fold_complex</t>
         </is>
       </c>
       <c r="D94" t="inlineStr">
         <is>
-          <t>neutral</t>
+          <t>destab</t>
         </is>
       </c>
       <c r="E94" t="inlineStr">
@@ -4820,17 +4819,17 @@
       </c>
       <c r="G94" t="inlineStr">
         <is>
-          <t>VCB assembly preserved while HIF binding is abolished (beta-domain HIF face, not the ElonginC face)</t>
+          <t>Disrupts VCB complex assembly</t>
         </is>
       </c>
       <c r="H94" t="inlineStr">
         <is>
-          <t>Ohh 2000</t>
+          <t>Stebbins 1999 Science</t>
         </is>
       </c>
       <c r="I94" t="inlineStr">
         <is>
-          <t>[50]</t>
+          <t>[49]</t>
         </is>
       </c>
     </row>
@@ -4847,7 +4846,7 @@
       </c>
       <c r="C95" t="inlineStr">
         <is>
-          <t>fold_complex</t>
+          <t>binding</t>
         </is>
       </c>
       <c r="D95" t="inlineStr">
@@ -4884,17 +4883,17 @@
     <row r="96">
       <c r="A96" t="inlineStr">
         <is>
-          <t>vwf_gpiba</t>
+          <t>vhl_elonginc</t>
         </is>
       </c>
       <c r="B96" t="inlineStr">
         <is>
-          <t>A1381T</t>
+          <t>Y98H</t>
         </is>
       </c>
       <c r="C96" t="inlineStr">
         <is>
-          <t>binding</t>
+          <t>fold_complex</t>
         </is>
       </c>
       <c r="D96" t="inlineStr">
@@ -4904,7 +4903,7 @@
       </c>
       <c r="E96" t="inlineStr">
         <is>
-          <t>E1_quantitative_energetic</t>
+          <t>E3_qualitative_experimental</t>
         </is>
       </c>
       <c r="F96" t="inlineStr">
@@ -4914,17 +4913,17 @@
       </c>
       <c r="G96" t="inlineStr">
         <is>
-          <t>Binding-competent by SPR</t>
+          <t>VCB assembly preserved while HIF binding is abolished (beta-domain HIF face, not the ElonginC face)</t>
         </is>
       </c>
       <c r="H96" t="inlineStr">
         <is>
-          <t>Tischer / Moon-Tasson / Auton 2025 J Thromb Haemost 23(4):1215-1228 (PMID 39756657); CD/DSC + SPR + shear-flow</t>
+          <t>Ohh 2000</t>
         </is>
       </c>
       <c r="I96" t="inlineStr">
         <is>
-          <t>[52]</t>
+          <t>[50]</t>
         </is>
       </c>
     </row>
@@ -4941,7 +4940,7 @@
       </c>
       <c r="C97" t="inlineStr">
         <is>
-          <t>fold_complex</t>
+          <t>binding</t>
         </is>
       </c>
       <c r="D97" t="inlineStr">
@@ -4951,17 +4950,17 @@
       </c>
       <c r="E97" t="inlineStr">
         <is>
-          <t>E5_inferred_no_axis_assay</t>
+          <t>E1_quantitative_energetic</t>
         </is>
       </c>
       <c r="F97" t="inlineStr">
         <is>
-          <t>inferred</t>
+          <t>direct</t>
         </is>
       </c>
       <c r="G97" t="inlineStr">
         <is>
-          <t>No assembly-context stability measurement; token inferred from the intact monomer fold</t>
+          <t>Binding-competent by SPR</t>
         </is>
       </c>
       <c r="H97" t="inlineStr">
@@ -4988,7 +4987,7 @@
       </c>
       <c r="C98" t="inlineStr">
         <is>
-          <t>monomer</t>
+          <t>fold_complex</t>
         </is>
       </c>
       <c r="D98" t="inlineStr">
@@ -4998,17 +4997,17 @@
       </c>
       <c r="E98" t="inlineStr">
         <is>
-          <t>E1_quantitative_energetic</t>
+          <t>E5_inferred_no_axis_assay</t>
         </is>
       </c>
       <c r="F98" t="inlineStr">
         <is>
-          <t>direct</t>
+          <t>inferred</t>
         </is>
       </c>
       <c r="G98" t="inlineStr">
         <is>
-          <t>Natively folded, WT-like Tm</t>
+          <t>No assembly-context stability measurement; token inferred from the intact monomer fold</t>
         </is>
       </c>
       <c r="H98" t="inlineStr">
@@ -5030,17 +5029,17 @@
       </c>
       <c r="B99" t="inlineStr">
         <is>
-          <t>R1334Q</t>
+          <t>A1381T</t>
         </is>
       </c>
       <c r="C99" t="inlineStr">
         <is>
-          <t>binding</t>
+          <t>monomer</t>
         </is>
       </c>
       <c r="D99" t="inlineStr">
         <is>
-          <t>destab</t>
+          <t>neutral</t>
         </is>
       </c>
       <c r="E99" t="inlineStr">
@@ -5055,7 +5054,7 @@
       </c>
       <c r="G99" t="inlineStr">
         <is>
-          <t>GPIba binding lost by SPR and shear-flow adhesion</t>
+          <t>Natively folded, WT-like Tm</t>
         </is>
       </c>
       <c r="H99" t="inlineStr">
@@ -5082,27 +5081,27 @@
       </c>
       <c r="C100" t="inlineStr">
         <is>
-          <t>fold_complex</t>
+          <t>binding</t>
         </is>
       </c>
       <c r="D100" t="inlineStr">
         <is>
-          <t>neutral</t>
+          <t>destab</t>
         </is>
       </c>
       <c r="E100" t="inlineStr">
         <is>
-          <t>E5_inferred_no_axis_assay</t>
+          <t>E1_quantitative_energetic</t>
         </is>
       </c>
       <c r="F100" t="inlineStr">
         <is>
-          <t>inferred</t>
+          <t>direct</t>
         </is>
       </c>
       <c r="G100" t="inlineStr">
         <is>
-          <t>No assembly-context stability measurement; token inferred from the intact monomer fold</t>
+          <t>GPIba binding lost by SPR and shear-flow adhesion</t>
         </is>
       </c>
       <c r="H100" t="inlineStr">
@@ -5129,35 +5128,82 @@
       </c>
       <c r="C101" t="inlineStr">
         <is>
+          <t>fold_complex</t>
+        </is>
+      </c>
+      <c r="D101" t="inlineStr">
+        <is>
+          <t>neutral</t>
+        </is>
+      </c>
+      <c r="E101" t="inlineStr">
+        <is>
+          <t>E5_inferred_no_axis_assay</t>
+        </is>
+      </c>
+      <c r="F101" t="inlineStr">
+        <is>
+          <t>inferred</t>
+        </is>
+      </c>
+      <c r="G101" t="inlineStr">
+        <is>
+          <t>No assembly-context stability measurement; token inferred from the intact monomer fold</t>
+        </is>
+      </c>
+      <c r="H101" t="inlineStr">
+        <is>
+          <t>Tischer / Moon-Tasson / Auton 2025 J Thromb Haemost 23(4):1215-1228 (PMID 39756657); CD/DSC + SPR + shear-flow</t>
+        </is>
+      </c>
+      <c r="I101" t="inlineStr">
+        <is>
+          <t>[52]</t>
+        </is>
+      </c>
+    </row>
+    <row r="102">
+      <c r="A102" t="inlineStr">
+        <is>
+          <t>vwf_gpiba</t>
+        </is>
+      </c>
+      <c r="B102" t="inlineStr">
+        <is>
+          <t>R1334Q</t>
+        </is>
+      </c>
+      <c r="C102" t="inlineStr">
+        <is>
           <t>monomer</t>
         </is>
       </c>
-      <c r="D101" t="inlineStr">
-        <is>
-          <t>neutral</t>
-        </is>
-      </c>
-      <c r="E101" t="inlineStr">
+      <c r="D102" t="inlineStr">
+        <is>
+          <t>neutral</t>
+        </is>
+      </c>
+      <c r="E102" t="inlineStr">
         <is>
           <t>E1_quantitative_energetic</t>
         </is>
       </c>
-      <c r="F101" t="inlineStr">
-        <is>
-          <t>direct</t>
-        </is>
-      </c>
-      <c r="G101" t="inlineStr">
+      <c r="F102" t="inlineStr">
+        <is>
+          <t>direct</t>
+        </is>
+      </c>
+      <c r="G102" t="inlineStr">
         <is>
           <t>Natively folded with modestly reduced Tm -- below the destabilization threshold</t>
         </is>
       </c>
-      <c r="H101" t="inlineStr">
+      <c r="H102" t="inlineStr">
         <is>
           <t>Tischer / Moon-Tasson / Auton 2025 J Thromb Haemost 23(4):1215-1228 (PMID 39756657); CD/DSC + SPR + shear-flow</t>
         </is>
       </c>
-      <c r="I101" t="inlineStr">
+      <c r="I102" t="inlineStr">
         <is>
           <t>[52]</t>
         </is>
@@ -5184,7 +5230,6 @@
         </is>
       </c>
     </row>
-    <row r="2"/>
     <row r="3">
       <c r="A3" s="1" t="inlineStr">
         <is>

--- a/submission/COMAVI_v7.15_SI/S1_Table.xlsx
+++ b/submission/COMAVI_v7.15_SI/S1_Table.xlsx
@@ -1633,7 +1633,7 @@
       </c>
       <c r="I26" t="inlineStr">
         <is>
-          <t>[51]</t>
+          <t>[53]</t>
         </is>
       </c>
     </row>
@@ -1680,7 +1680,7 @@
       </c>
       <c r="I27" t="inlineStr">
         <is>
-          <t>[51]</t>
+          <t>[53]</t>
         </is>
       </c>
     </row>
@@ -1727,7 +1727,7 @@
       </c>
       <c r="I28" t="inlineStr">
         <is>
-          <t>[51]</t>
+          <t>[53]</t>
         </is>
       </c>
     </row>
@@ -1774,7 +1774,7 @@
       </c>
       <c r="I29" t="inlineStr">
         <is>
-          <t>[51]</t>
+          <t>[53]</t>
         </is>
       </c>
     </row>
@@ -1821,7 +1821,7 @@
       </c>
       <c r="I30" t="inlineStr">
         <is>
-          <t>[51]</t>
+          <t>[53]</t>
         </is>
       </c>
     </row>
@@ -1868,7 +1868,7 @@
       </c>
       <c r="I31" t="inlineStr">
         <is>
-          <t>[51]</t>
+          <t>[53]</t>
         </is>
       </c>
     </row>
@@ -1915,7 +1915,7 @@
       </c>
       <c r="I32" t="inlineStr">
         <is>
-          <t>[51]</t>
+          <t>[53]</t>
         </is>
       </c>
     </row>
@@ -1962,7 +1962,7 @@
       </c>
       <c r="I33" t="inlineStr">
         <is>
-          <t>[51]</t>
+          <t>[53]</t>
         </is>
       </c>
     </row>
@@ -2009,7 +2009,7 @@
       </c>
       <c r="I34" t="inlineStr">
         <is>
-          <t>[51]</t>
+          <t>[53]</t>
         </is>
       </c>
     </row>
@@ -2056,7 +2056,7 @@
       </c>
       <c r="I35" t="inlineStr">
         <is>
-          <t>[53]</t>
+          <t>[55]</t>
         </is>
       </c>
     </row>
@@ -2103,7 +2103,7 @@
       </c>
       <c r="I36" t="inlineStr">
         <is>
-          <t>[53]</t>
+          <t>[55]</t>
         </is>
       </c>
     </row>
@@ -2150,7 +2150,7 @@
       </c>
       <c r="I37" t="inlineStr">
         <is>
-          <t>[53]</t>
+          <t>[55]</t>
         </is>
       </c>
     </row>
@@ -2197,7 +2197,7 @@
       </c>
       <c r="I38" t="inlineStr">
         <is>
-          <t>[56]</t>
+          <t>[58]</t>
         </is>
       </c>
     </row>
@@ -2244,7 +2244,7 @@
       </c>
       <c r="I39" t="inlineStr">
         <is>
-          <t>[56]</t>
+          <t>[58]</t>
         </is>
       </c>
     </row>
@@ -2291,7 +2291,7 @@
       </c>
       <c r="I40" t="inlineStr">
         <is>
-          <t>[54]</t>
+          <t>[56]</t>
         </is>
       </c>
     </row>
@@ -2338,7 +2338,7 @@
       </c>
       <c r="I41" t="inlineStr">
         <is>
-          <t>[54]</t>
+          <t>[56]</t>
         </is>
       </c>
     </row>
@@ -2385,7 +2385,7 @@
       </c>
       <c r="I42" t="inlineStr">
         <is>
-          <t>[54]</t>
+          <t>[56]</t>
         </is>
       </c>
     </row>
@@ -2432,7 +2432,7 @@
       </c>
       <c r="I43" t="inlineStr">
         <is>
-          <t>[54]</t>
+          <t>[56]</t>
         </is>
       </c>
     </row>
@@ -2479,7 +2479,7 @@
       </c>
       <c r="I44" t="inlineStr">
         <is>
-          <t>[54]</t>
+          <t>[56]</t>
         </is>
       </c>
     </row>
@@ -2526,7 +2526,7 @@
       </c>
       <c r="I45" t="inlineStr">
         <is>
-          <t>[54]</t>
+          <t>[56]</t>
         </is>
       </c>
     </row>
@@ -2573,7 +2573,7 @@
       </c>
       <c r="I46" t="inlineStr">
         <is>
-          <t>[54]</t>
+          <t>[56]</t>
         </is>
       </c>
     </row>
@@ -2620,7 +2620,7 @@
       </c>
       <c r="I47" t="inlineStr">
         <is>
-          <t>[54]</t>
+          <t>[56]</t>
         </is>
       </c>
     </row>
@@ -2808,7 +2808,7 @@
       </c>
       <c r="I51" t="inlineStr">
         <is>
-          <t>[57]</t>
+          <t>[59]</t>
         </is>
       </c>
     </row>
@@ -2855,7 +2855,7 @@
       </c>
       <c r="I52" t="inlineStr">
         <is>
-          <t>[57]</t>
+          <t>[59]</t>
         </is>
       </c>
     </row>
@@ -2902,7 +2902,7 @@
       </c>
       <c r="I53" t="inlineStr">
         <is>
-          <t>[57]</t>
+          <t>[59]</t>
         </is>
       </c>
     </row>
@@ -2949,7 +2949,7 @@
       </c>
       <c r="I54" t="inlineStr">
         <is>
-          <t>[33]</t>
+          <t>[34]</t>
         </is>
       </c>
     </row>
@@ -2996,7 +2996,7 @@
       </c>
       <c r="I55" t="inlineStr">
         <is>
-          <t>[33]</t>
+          <t>[34]</t>
         </is>
       </c>
     </row>
@@ -3043,7 +3043,7 @@
       </c>
       <c r="I56" t="inlineStr">
         <is>
-          <t>see evidence_citation</t>
+          <t>[33]</t>
         </is>
       </c>
     </row>
@@ -3090,7 +3090,7 @@
       </c>
       <c r="I57" t="inlineStr">
         <is>
-          <t>[34]</t>
+          <t>[35]</t>
         </is>
       </c>
     </row>
@@ -3372,7 +3372,7 @@
       </c>
       <c r="I63" t="inlineStr">
         <is>
-          <t>[35]</t>
+          <t>[36]</t>
         </is>
       </c>
     </row>
@@ -3419,7 +3419,7 @@
       </c>
       <c r="I64" t="inlineStr">
         <is>
-          <t>[35]</t>
+          <t>[36]</t>
         </is>
       </c>
     </row>
@@ -3466,7 +3466,7 @@
       </c>
       <c r="I65" t="inlineStr">
         <is>
-          <t>[35]</t>
+          <t>[36]</t>
         </is>
       </c>
     </row>
@@ -3513,7 +3513,7 @@
       </c>
       <c r="I66" t="inlineStr">
         <is>
-          <t>[37, 38]</t>
+          <t>[38, 39]</t>
         </is>
       </c>
     </row>
@@ -3560,7 +3560,7 @@
       </c>
       <c r="I67" t="inlineStr">
         <is>
-          <t>[37, 38]</t>
+          <t>[38, 39]</t>
         </is>
       </c>
     </row>
@@ -3607,7 +3607,7 @@
       </c>
       <c r="I68" t="inlineStr">
         <is>
-          <t>[37, 38]</t>
+          <t>[38, 39]</t>
         </is>
       </c>
     </row>
@@ -3654,7 +3654,7 @@
       </c>
       <c r="I69" t="inlineStr">
         <is>
-          <t>[37, 38]</t>
+          <t>[38, 39]</t>
         </is>
       </c>
     </row>
@@ -3701,7 +3701,7 @@
       </c>
       <c r="I70" t="inlineStr">
         <is>
-          <t>[37, 38]</t>
+          <t>[38, 39]</t>
         </is>
       </c>
     </row>
@@ -3748,7 +3748,7 @@
       </c>
       <c r="I71" t="inlineStr">
         <is>
-          <t>[37, 38]</t>
+          <t>[38, 39]</t>
         </is>
       </c>
     </row>
@@ -3795,7 +3795,7 @@
       </c>
       <c r="I72" t="inlineStr">
         <is>
-          <t>[40]</t>
+          <t>[41]</t>
         </is>
       </c>
     </row>
@@ -3842,7 +3842,7 @@
       </c>
       <c r="I73" t="inlineStr">
         <is>
-          <t>[40]</t>
+          <t>[41]</t>
         </is>
       </c>
     </row>
@@ -3889,7 +3889,7 @@
       </c>
       <c r="I74" t="inlineStr">
         <is>
-          <t>[40]</t>
+          <t>[41]</t>
         </is>
       </c>
     </row>
@@ -3936,7 +3936,7 @@
       </c>
       <c r="I75" t="inlineStr">
         <is>
-          <t>[40]</t>
+          <t>[41]</t>
         </is>
       </c>
     </row>
@@ -3983,7 +3983,7 @@
       </c>
       <c r="I76" t="inlineStr">
         <is>
-          <t>[41]</t>
+          <t>[42]</t>
         </is>
       </c>
     </row>
@@ -4030,7 +4030,7 @@
       </c>
       <c r="I77" t="inlineStr">
         <is>
-          <t>[41]</t>
+          <t>[42]</t>
         </is>
       </c>
     </row>
@@ -4077,7 +4077,7 @@
       </c>
       <c r="I78" t="inlineStr">
         <is>
-          <t>[41]</t>
+          <t>[42]</t>
         </is>
       </c>
     </row>
@@ -4124,7 +4124,7 @@
       </c>
       <c r="I79" t="inlineStr">
         <is>
-          <t>[57]</t>
+          <t>[59]</t>
         </is>
       </c>
     </row>
@@ -4171,7 +4171,7 @@
       </c>
       <c r="I80" t="inlineStr">
         <is>
-          <t>[57]</t>
+          <t>[59]</t>
         </is>
       </c>
     </row>
@@ -4218,7 +4218,7 @@
       </c>
       <c r="I81" t="inlineStr">
         <is>
-          <t>[57]</t>
+          <t>[59]</t>
         </is>
       </c>
     </row>
@@ -4265,7 +4265,7 @@
       </c>
       <c r="I82" t="inlineStr">
         <is>
-          <t>[61]</t>
+          <t>[63]</t>
         </is>
       </c>
     </row>
@@ -4312,7 +4312,7 @@
       </c>
       <c r="I83" t="inlineStr">
         <is>
-          <t>[61]</t>
+          <t>[63]</t>
         </is>
       </c>
     </row>
@@ -4359,7 +4359,7 @@
       </c>
       <c r="I84" t="inlineStr">
         <is>
-          <t>[61]</t>
+          <t>[63]</t>
         </is>
       </c>
     </row>
@@ -4406,7 +4406,7 @@
       </c>
       <c r="I85" t="inlineStr">
         <is>
-          <t>[43]</t>
+          <t>[44]</t>
         </is>
       </c>
     </row>
@@ -4453,7 +4453,7 @@
       </c>
       <c r="I86" t="inlineStr">
         <is>
-          <t>see evidence_citation</t>
+          <t>[46]</t>
         </is>
       </c>
     </row>
@@ -4500,7 +4500,7 @@
       </c>
       <c r="I87" t="inlineStr">
         <is>
-          <t>[45]</t>
+          <t>[47]</t>
         </is>
       </c>
     </row>
@@ -4547,7 +4547,7 @@
       </c>
       <c r="I88" t="inlineStr">
         <is>
-          <t>[47, 57]</t>
+          <t>[49, 59]</t>
         </is>
       </c>
     </row>
@@ -4594,7 +4594,7 @@
       </c>
       <c r="I89" t="inlineStr">
         <is>
-          <t>[47, 57]</t>
+          <t>[49, 59]</t>
         </is>
       </c>
     </row>
@@ -4641,7 +4641,7 @@
       </c>
       <c r="I90" t="inlineStr">
         <is>
-          <t>[47, 57]</t>
+          <t>[49, 59]</t>
         </is>
       </c>
     </row>
@@ -4688,7 +4688,7 @@
       </c>
       <c r="I91" t="inlineStr">
         <is>
-          <t>[46, 48]</t>
+          <t>[48, 50]</t>
         </is>
       </c>
     </row>
@@ -4730,12 +4730,12 @@
       </c>
       <c r="H92" t="inlineStr">
         <is>
-          <t>Kimura 2001 (PMID 11735257)</t>
+          <t>Takahashi-Yanaga 2001 (PMID 11735257)</t>
         </is>
       </c>
       <c r="I92" t="inlineStr">
         <is>
-          <t>[48]</t>
+          <t>[50]</t>
         </is>
       </c>
     </row>
@@ -4782,7 +4782,7 @@
       </c>
       <c r="I93" t="inlineStr">
         <is>
-          <t>[49]</t>
+          <t>[51]</t>
         </is>
       </c>
     </row>
@@ -4829,7 +4829,7 @@
       </c>
       <c r="I94" t="inlineStr">
         <is>
-          <t>[49]</t>
+          <t>[51]</t>
         </is>
       </c>
     </row>
@@ -4876,7 +4876,7 @@
       </c>
       <c r="I95" t="inlineStr">
         <is>
-          <t>[50]</t>
+          <t>[52]</t>
         </is>
       </c>
     </row>
@@ -4923,7 +4923,7 @@
       </c>
       <c r="I96" t="inlineStr">
         <is>
-          <t>[50]</t>
+          <t>[52]</t>
         </is>
       </c>
     </row>
@@ -4970,7 +4970,7 @@
       </c>
       <c r="I97" t="inlineStr">
         <is>
-          <t>[52]</t>
+          <t>[54]</t>
         </is>
       </c>
     </row>
@@ -5017,7 +5017,7 @@
       </c>
       <c r="I98" t="inlineStr">
         <is>
-          <t>[52]</t>
+          <t>[54]</t>
         </is>
       </c>
     </row>
@@ -5064,7 +5064,7 @@
       </c>
       <c r="I99" t="inlineStr">
         <is>
-          <t>[52]</t>
+          <t>[54]</t>
         </is>
       </c>
     </row>
@@ -5111,7 +5111,7 @@
       </c>
       <c r="I100" t="inlineStr">
         <is>
-          <t>[52]</t>
+          <t>[54]</t>
         </is>
       </c>
     </row>
@@ -5158,7 +5158,7 @@
       </c>
       <c r="I101" t="inlineStr">
         <is>
-          <t>[52]</t>
+          <t>[54]</t>
         </is>
       </c>
     </row>
@@ -5205,7 +5205,7 @@
       </c>
       <c r="I102" t="inlineStr">
         <is>
-          <t>[52]</t>
+          <t>[54]</t>
         </is>
       </c>
     </row>
@@ -5411,7 +5411,7 @@
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>[44]</t>
+          <t>[45]</t>
         </is>
       </c>
     </row>
@@ -5448,7 +5448,7 @@
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>[44]</t>
+          <t>[45]</t>
         </is>
       </c>
     </row>

--- a/submission/COMAVI_v7.15_SI/S1_Table.xlsx
+++ b/submission/COMAVI_v7.15_SI/S1_Table.xlsx
@@ -509,6 +509,7 @@
         </is>
       </c>
     </row>
+    <row r="2"/>
     <row r="3">
       <c r="A3" s="1" t="inlineStr">
         <is>
@@ -2986,7 +2987,7 @@
       </c>
       <c r="G55" t="inlineStr">
         <is>
-          <t>No assembly-context stability measurement; token inferred from the intact monomer fold</t>
+          <t>No assembly-context stability measurement; token inferred from proficient MMR and a surviving MLH1-PMS2 interaction, not from the isolated fold, which this source reports as destabilized</t>
         </is>
       </c>
       <c r="H55" t="inlineStr">
